--- a/ticket_order_forms/050_sports_event_ticket_purchase_form--ticket_order_forms.xlsx
+++ b/ticket_order_forms/050_sports_event_ticket_purchase_form--ticket_order_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -696,8 +696,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
-    <col width="37" customWidth="1" min="2" max="2"/>
-    <col width="37" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -725,12 +725,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'name'}</t>
+          <t>name</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Name'}</t>
+          <t>Name</t>
         </is>
       </c>
     </row>
@@ -742,12 +742,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'email'}</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Email'}</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
@@ -759,12 +759,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'phone'}</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Phone'}</t>
+          <t>Phone</t>
         </is>
       </c>
     </row>
@@ -776,12 +776,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'event_1'}</t>
+          <t>event_1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Event 1'}</t>
+          <t>Event 1</t>
         </is>
       </c>
     </row>
@@ -793,12 +793,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'event_2'}</t>
+          <t>event_2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Event 2'}</t>
+          <t>Event 2</t>
         </is>
       </c>
     </row>
@@ -810,12 +810,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'event_3'}</t>
+          <t>event_3</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Event 3'}</t>
+          <t>Event 3</t>
         </is>
       </c>
     </row>
@@ -827,12 +827,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'credit_card'}</t>
+          <t>credit_card</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Credit Card'}</t>
+          <t>Credit Card</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'paypal'}</t>
+          <t>paypal</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'PayPal'}</t>
+          <t>PayPal</t>
         </is>
       </c>
     </row>
@@ -861,12 +861,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'bank_transfer'}</t>
+          <t>bank_transfer</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Bank Transfer'}</t>
+          <t>Bank Transfer</t>
         </is>
       </c>
     </row>
